--- a/Excel-files/customer_createBulk_vu1.xlsx
+++ b/Excel-files/customer_createBulk_vu1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS01503\Documents\load testing Script-BSS\Excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0E5CFA-1C8D-456D-8C77-31C00C6F6830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C377689-930C-43D8-BF2F-CE3ECA48C5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19400" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="582">
   <si>
     <t>DHAKA</t>
   </si>
@@ -1831,17 +1831,23 @@
     <t>INACTIVE</t>
   </si>
   <si>
-    <t>Faria11</t>
-  </si>
-  <si>
-    <t>Faria12</t>
+    <t>Anika1</t>
+  </si>
+  <si>
+    <t>Anika2</t>
+  </si>
+  <si>
+    <t>Anika3</t>
+  </si>
+  <si>
+    <t>Anika4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1858,9 +1864,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1910,7 +1922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1924,7 +1936,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2240,7 +2251,7 @@
     <col min="4" max="4" width="36.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.1796875" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="41" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -2261,7 +2272,7 @@
     <col min="25" max="27" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>540</v>
       </c>
@@ -2335,7 +2346,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>564</v>
       </c>
@@ -2385,7 +2396,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>564</v>
       </c>
@@ -2398,7 +2409,7 @@
       <c r="D3" t="s">
         <v>567</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>579</v>
       </c>
       <c r="F3" t="s">
@@ -2435,8 +2446,106 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B4" t="s">
+        <v>565</v>
+      </c>
+      <c r="C4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D4" t="s">
+        <v>567</v>
+      </c>
+      <c r="E4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="H4" t="s">
+        <v>570</v>
+      </c>
+      <c r="I4" t="s">
+        <v>570</v>
+      </c>
+      <c r="J4" t="s">
+        <v>571</v>
+      </c>
+      <c r="K4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" t="s">
+        <v>191</v>
+      </c>
+      <c r="N4" t="s">
+        <v>572</v>
+      </c>
+      <c r="O4" t="s">
+        <v>573</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D5" t="s">
+        <v>567</v>
+      </c>
+      <c r="E5" t="s">
+        <v>581</v>
+      </c>
+      <c r="F5" t="s">
+        <v>568</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="H5" t="s">
+        <v>570</v>
+      </c>
+      <c r="I5" t="s">
+        <v>570</v>
+      </c>
+      <c r="J5" t="s">
+        <v>571</v>
+      </c>
+      <c r="K5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>191</v>
+      </c>
+      <c r="N5" t="s">
+        <v>572</v>
+      </c>
+      <c r="O5" t="s">
+        <v>573</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+    </row>
     <row r="6" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -12455,6 +12564,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
